--- a/reports/tables/bootstrap_ci.xlsx
+++ b/reports/tables/bootstrap_ci.xlsx
@@ -467,20 +467,20 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6831</v>
+        <v>0.6803</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6833</v>
+        <v>0.6804</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6091</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7526</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.6831 (0.6091–0.7526)</t>
+          <t>0.6803 (0.6064–0.7535)</t>
         </is>
       </c>
     </row>
@@ -491,20 +491,20 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1098</v>
+        <v>0.1175</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1186</v>
+        <v>0.1276</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0834</v>
       </c>
       <c r="E3" t="n">
-        <v>0.179</v>
+        <v>0.1973</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.1098 (0.0778–0.179)</t>
+          <t>0.1175 (0.0834–0.1973)</t>
         </is>
       </c>
     </row>
@@ -515,20 +515,20 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2329</v>
+        <v>0.2325</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2329</v>
+        <v>0.2325</v>
       </c>
       <c r="D4" t="n">
-        <v>0.226</v>
+        <v>0.2261</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2393</v>
+        <v>0.2384</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.2329 (0.226–0.2393)</t>
+          <t>0.2325 (0.2261–0.2384)</t>
         </is>
       </c>
     </row>
@@ -539,20 +539,20 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0669</v>
+        <v>0.0679</v>
       </c>
       <c r="C5" t="n">
-        <v>0.067</v>
+        <v>0.0679</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0502</v>
+        <v>0.0511</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0838</v>
+        <v>0.0851</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.0669 (0.0502–0.0838)</t>
+          <t>0.0679 (0.0511–0.0851)</t>
         </is>
       </c>
     </row>
@@ -563,20 +563,20 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7805</v>
+        <v>0.7317</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7809</v>
+        <v>0.7323</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6444</v>
+        <v>0.5869</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9</v>
+        <v>0.8667</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.7805 (0.6444–0.9)</t>
+          <t>0.7317 (0.5869–0.8667)</t>
         </is>
       </c>
     </row>
@@ -587,20 +587,20 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.5522</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5379</v>
+        <v>0.552</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4858</v>
+        <v>0.5018</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5919</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.5378 (0.4858–0.5919)</t>
+          <t>0.5522 (0.5018–0.6033)</t>
         </is>
       </c>
     </row>
@@ -611,20 +611,20 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9708</v>
+        <v>0.9654</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9708</v>
+        <v>0.9654</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9509</v>
+        <v>0.944</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9873</v>
+        <v>0.9839</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.9708 (0.9509–0.9873)</t>
+          <t>0.9654 (0.944–0.9839)</t>
         </is>
       </c>
     </row>
@@ -635,20 +635,20 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1107</v>
+        <v>0.1075</v>
       </c>
       <c r="C9" t="n">
-        <v>0.111</v>
+        <v>0.1078</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0775</v>
+        <v>0.0746</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1463</v>
+        <v>0.1453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.1107 (0.0775–0.1463)</t>
+          <t>0.1075 (0.0746–0.1453)</t>
         </is>
       </c>
     </row>
